--- a/docs/reminders.xlsx
+++ b/docs/reminders.xlsx
@@ -714,7 +714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -738,6 +738,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1114,6 +1115,33 @@
       <c r="E17" s="5" t="inlineStr">
         <is>
           <t>If you skip this, magic-link emails open the browser instead of the mobile app on Android.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>First paying coach signs up via Stripe (real subscription, not test mode)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BEFORE that coach can hit the 30-day point and request deletion, ship the Stripe pause/resume orchestration edge function. The DB-side deletion flow exists already but does NOT touch Stripe yet — paying coaches will keep getting charged during grace unless this lands.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>docs/launch_checklist.xlsx → Phase 1 → Billing → Stripe pause/resume row</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Blocking for billing correctness once paying coaches exist. Non-blocking today (no real-money subs yet).</t>
         </is>
       </c>
     </row>
